--- a/cad/redesign/hobby_servo/v1.0/BOM_hobby_servo_v1.0.xlsx
+++ b/cad/redesign/hobby_servo/v1.0/BOM_hobby_servo_v1.0.xlsx
@@ -497,7 +497,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Microduck 일반 서보 v1.0 BOM — 어셈블리 1_microduck_hobby_servo_v1.0 (Fusion 개인/microduck_hobby_servo_v1.0)</t>
+          <t>Microduck hobby_servo v1.0 BOM — 어셈블리 1_microduck_hobby_servo_v1.0 (Fusion 개인/microduck_hobby_servo_v1.0)</t>
         </is>
       </c>
     </row>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>얇은 볼베어링 30×37×4 (고관절 yaw 혼 둘레)</t>
+          <t>얇은 볼베어링 30×37×4 (yaw 관절 혼 둘레)</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
